--- a/outputs/results/all_results_ensemble.xlsx
+++ b/outputs/results/all_results_ensemble.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard_ภาพรวม" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Detailed_Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_ภาพรวม" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Results" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed_Results'!$A$1:$F$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed_Results'!$A$1:$F$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -618,10 +618,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="124" customWidth="1" min="1" max="1"/>
+    <col width="116" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>สร้างรายงานเมื่อ: 2026-10-21 00:33:09 | โมเดลที่ใช้ตรวจ: Dual-Ensemble MLP (93.94%) | ตรวจทั้งหมด: 9 แผ่น | รวม 180 ข้อ</t>
+          <t>สร้างรายงานเมื่อ: 2026-10-26 14:43:01 | โมเดลที่ใช้ตรวจ: Dual-Ensemble MLP | ตรวจทั้งหมด: 12 แผ่น | รวม 240 ข้อ</t>
         </is>
       </c>
     </row>
@@ -676,27 +676,27 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>9 แผ่น</t>
+          <t>12 แผ่น</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>180 ข้อ</t>
+          <t>240 ข้อ</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>3,600 ตัว</t>
+          <t>4,800 ตัว</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>93.94%</t>
+          <t>93.04%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>110 ข้อ</t>
+          <t>159 ข้อ</t>
         </is>
       </c>
     </row>
@@ -760,17 +760,17 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>99.75%</t>
+          <t>99.50%</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>0.990</t>
+          <t>0.989</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>8 ข้อ</t>
+          <t>9 ข้อ</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>80.75%</t>
+          <t>77.75%</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>0.975</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>5 ข้อ</t>
+          <t>6 ข้อ</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>93.50%</t>
+          <t>93.25%</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>0.978</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>94.25%</t>
+          <t>94.75%</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>0.970</t>
+          <t>0.969</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -991,17 +991,17 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>93.00%</t>
+          <t>94.00%</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>0.950</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>17 ข้อ</t>
+          <t>18 ข้อ</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -1024,20 +1024,119 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>92.50%</t>
+          <t>89.50%</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>0.987</t>
+          <t>0.950</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>8 ข้อ</t>
+          <t>17 ข้อ</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>English &amp; Tech (ชุดที่ 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>82.25%</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>0.927</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>19 ข้อ</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>English &amp; Tech (ชุดที่ 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>95.25%</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>0.978</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>12 ข้อ</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>English &amp; Tech (ชุดที่ 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>0.991</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>6 ข้อ</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>English &amp; Tech (ชุดที่ 1)</t>
         </is>
@@ -1057,10 +1156,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -1137,18 +1236,18 @@
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>JUMPS-OVER-LAZY-DOG-</t>
+          <t>JUMPS-OVER-LAZY-COG-</t>
         </is>
       </c>
       <c r="D3" s="19" t="n">
-        <v>0.992</v>
+        <v>0.975</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -1657,11 +1756,11 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>JUQMS-OVER-LAZY-DOG-</t>
+          <t>JUQMS-OVEB-LAZY-DOG-</t>
         </is>
       </c>
       <c r="D23" s="19" t="n">
-        <v>0.93</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E23" s="19" t="n">
         <v>0.499</v>
@@ -1735,11 +1834,11 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>SPHUNX-OF-BLACK-GEM-</t>
+          <t>SPHUNX-OF-BLACK-GFM-</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>0.965</v>
+        <v>0.971</v>
       </c>
       <c r="E26" s="15" t="n">
         <v>0.5</v>
@@ -1787,11 +1886,11 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>BR-SHI-LEPHYMS-ELOL-</t>
+          <t>BB-SHI-LEPHYMS-ELOL-</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>0.908</v>
+        <v>0.913</v>
       </c>
       <c r="E28" s="15" t="n">
         <v>0.499</v>
@@ -1839,11 +1938,11 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>MACHINEWLEARNING-AJ-</t>
+          <t>MACHINE-LEABNING-AJ-</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.958</v>
+        <v>0.97</v>
       </c>
       <c r="E30" s="15" t="n">
         <v>0.5</v>
@@ -1865,11 +1964,11 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>DEEP-NEURAU-AFTWOPKX</t>
+          <t>DEEP-NEUBAU-AFTWOPKX</t>
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0.887</v>
+        <v>0.879</v>
       </c>
       <c r="E31" s="19" t="n">
         <v>0.5</v>
@@ -1891,14 +1990,14 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>-MAGE-DATA-EEZFCT-CK</t>
+          <t>-MAGE-DATA-FFZFCT-CK</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.873</v>
+        <v>0.841</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>0.5</v>
+        <v>0.466</v>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
@@ -1943,11 +2042,11 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>SDART-CCM-RECOGNIZE-</t>
+          <t>SDART-CCM-BECCGNIZE-</t>
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.904</v>
+        <v>0.913</v>
       </c>
       <c r="E34" s="15" t="n">
         <v>0.5</v>
@@ -1999,7 +2098,7 @@
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.88</v>
+        <v>0.881</v>
       </c>
       <c r="E36" s="15" t="n">
         <v>0.5</v>
@@ -2021,11 +2120,11 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>HELLC-WOFLD-WELOCME-</t>
+          <t>HELLC-WOFLD-WFLOCME-</t>
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>0.887</v>
+        <v>0.894</v>
       </c>
       <c r="E37" s="19" t="n">
         <v>0.46</v>
@@ -2047,14 +2146,14 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>KUOWLUCCECIS-PQLEB--</t>
+          <t>KUOWL-CCECIS-PQLEB--</t>
         </is>
       </c>
       <c r="D38" s="15" t="n">
-        <v>0.884</v>
+        <v>0.919</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.301</v>
+        <v>0.454</v>
       </c>
       <c r="F38" s="16" t="inlineStr">
         <is>
@@ -2073,14 +2172,14 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>FIND-FXTRA-EINE-GOLD</t>
+          <t>FIND-FXTBA-EINF-GOLD</t>
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>0.931</v>
+        <v>0.917</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>0.499</v>
+        <v>0.419</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -2099,11 +2198,11 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>ZERQ-QNE--YG-SIX-TEN</t>
+          <t>ZEBQ-QNE--YG-SIX-TEN</t>
         </is>
       </c>
       <c r="D40" s="15" t="n">
-        <v>0.891</v>
+        <v>0.882</v>
       </c>
       <c r="E40" s="15" t="n">
         <v>0.5</v>
@@ -2125,11 +2224,11 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>ABCDEFGHIJKL-NOPGPOT</t>
+          <t>ABCDEFGHIJKL-NCPGPOT</t>
         </is>
       </c>
       <c r="D41" s="19" t="n">
-        <v>0.916</v>
+        <v>0.899</v>
       </c>
       <c r="E41" s="19" t="n">
         <v>0.497</v>
@@ -2177,14 +2276,14 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>JUMPS-OVER-LAZY-DOG-</t>
+          <t>JUMPS-OVEB-LAZY-DOG-</t>
         </is>
       </c>
       <c r="D43" s="19" t="n">
-        <v>0.989</v>
+        <v>0.996</v>
       </c>
       <c r="E43" s="19" t="n">
-        <v>0.85</v>
+        <v>0.922</v>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
@@ -2229,11 +2328,11 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>EIVE-DOZEN-LIQUOR-JU</t>
+          <t>FIVE-DOZEN-LIQUOR-JU</t>
         </is>
       </c>
       <c r="D45" s="19" t="n">
-        <v>0.979</v>
+        <v>0.986</v>
       </c>
       <c r="E45" s="19" t="n">
         <v>0.725</v>
@@ -2623,10 +2722,10 @@
         </is>
       </c>
       <c r="D60" s="15" t="n">
-        <v>0.993</v>
+        <v>0.994</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="F60" s="20" t="inlineStr">
         <is>
@@ -3035,14 +3134,14 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>ARTIEICIAL-SYSTEM-OK</t>
+          <t>ARTIFICIAL-SYSTEM-OK</t>
         </is>
       </c>
       <c r="D76" s="15" t="n">
-        <v>0.993</v>
+        <v>0.998</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.85</v>
+        <v>0.964</v>
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
@@ -3165,18 +3264,18 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>ABCDEFGHIJKLMNOPQRST</t>
+          <t>ABCDEFGHIJKLMNCPQRST</t>
         </is>
       </c>
       <c r="D81" s="19" t="n">
-        <v>0.993</v>
+        <v>0.98</v>
       </c>
       <c r="E81" s="19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F81" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.607</v>
+      </c>
+      <c r="F81" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -3217,18 +3316,18 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>JUMPS-OVER-LAZY-DOG-</t>
+          <t>JUMPS-OVFR-LAZY-DOG-</t>
         </is>
       </c>
       <c r="D83" s="19" t="n">
-        <v>0.992</v>
+        <v>0.974</v>
       </c>
       <c r="E83" s="19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F83" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.502</v>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -3243,18 +3342,18 @@
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>PACK-MYXBOX-WITH-TEA</t>
+          <t>PACK-MY-BOX-WITH-TEA</t>
         </is>
       </c>
       <c r="D84" s="15" t="n">
-        <v>0.956</v>
+        <v>0.995</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="F84" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0.89</v>
+      </c>
+      <c r="F84" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -3503,11 +3602,11 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>SMAR--OCR-RECOGNIZF-</t>
+          <t>SMART-OCR-RECOGNIZF-</t>
         </is>
       </c>
       <c r="D94" s="15" t="n">
-        <v>0.963</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E94" s="15" t="n">
         <v>0.5</v>
@@ -3581,11 +3680,11 @@
       </c>
       <c r="C97" s="18" t="inlineStr">
         <is>
-          <t>HELLO-WORLO-NELCOMF-</t>
+          <t>HFLLO-WORLO-NELCOMF-</t>
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>0.976</v>
+        <v>0.983</v>
       </c>
       <c r="E97" s="19" t="n">
         <v>0.679</v>
@@ -3633,11 +3732,11 @@
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>P-ND-EYTRA-FIND-GOLD</t>
+          <t>P-ND-FYTRA-FIND-GOLD</t>
         </is>
       </c>
       <c r="D99" s="19" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.944</v>
       </c>
       <c r="E99" s="19" t="n">
         <v>0.383</v>
@@ -3711,7 +3810,7 @@
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>THE-QUTCK-BROWN-FOX-</t>
+          <t>THF-QUTCK-BROWN-FOX-</t>
         </is>
       </c>
       <c r="D102" s="15" t="n">
@@ -3971,11 +4070,11 @@
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>TMAG--DATA-DETECT-OK</t>
+          <t>TMAGE-DATA-DETECT-OK</t>
         </is>
       </c>
       <c r="D112" s="15" t="n">
-        <v>0.973</v>
+        <v>0.971</v>
       </c>
       <c r="E112" s="15" t="n">
         <v>0.508</v>
@@ -3997,7 +4096,7 @@
       </c>
       <c r="C113" s="18" t="inlineStr">
         <is>
-          <t>P-THON-OPENCV-ROBOT-</t>
+          <t>PVTHON-OPENCV-ROBOT-</t>
         </is>
       </c>
       <c r="D113" s="19" t="n">
@@ -4153,11 +4252,11 @@
       </c>
       <c r="C119" s="18" t="inlineStr">
         <is>
-          <t>EIND-EXTRA-FIND-GOLD</t>
+          <t>FIND-EXTRA-FIND-GOLD</t>
         </is>
       </c>
       <c r="D119" s="19" t="n">
-        <v>0.978</v>
+        <v>0.984</v>
       </c>
       <c r="E119" s="19" t="n">
         <v>0.8169999999999999</v>
@@ -4205,11 +4304,11 @@
       </c>
       <c r="C121" s="18" t="inlineStr">
         <is>
-          <t>ARCDEFGHIJKLMNOPORST</t>
+          <t>ABCDEFGHIJKLMNOPORST</t>
         </is>
       </c>
       <c r="D121" s="19" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.922</v>
       </c>
       <c r="E121" s="19" t="n">
         <v>0.5</v>
@@ -4803,14 +4902,14 @@
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>EACK-MY-BCXXWITH-TEA</t>
+          <t>EACK-MY-BCX-WITH-TEA</t>
         </is>
       </c>
       <c r="D144" s="15" t="n">
-        <v>0.926</v>
+        <v>0.954</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0.428</v>
+        <v>0.511</v>
       </c>
       <c r="F144" s="16" t="inlineStr">
         <is>
@@ -4829,11 +4928,11 @@
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>EIVE-DOZEN-LIGUOR-QU</t>
+          <t>FIVE-DOZEN-LIGUOR-QU</t>
         </is>
       </c>
       <c r="D145" s="19" t="n">
-        <v>0.918</v>
+        <v>0.906</v>
       </c>
       <c r="E145" s="19" t="n">
         <v>0.5</v>
@@ -4881,14 +4980,14 @@
       </c>
       <c r="C147" s="18" t="inlineStr">
         <is>
-          <t>JUDGE-MY-VOWKQUICKLY</t>
+          <t>JUDGE-MY-VOW-QUICKLY</t>
         </is>
       </c>
       <c r="D147" s="19" t="n">
-        <v>0.95</v>
+        <v>0.979</v>
       </c>
       <c r="E147" s="19" t="n">
-        <v>0.405</v>
+        <v>0.674</v>
       </c>
       <c r="F147" s="16" t="inlineStr">
         <is>
@@ -5011,11 +5110,11 @@
       </c>
       <c r="C152" s="14" t="inlineStr">
         <is>
-          <t>IHAGE-DATA-DETECT-OK</t>
+          <t>IHAGF-DATA-DETECT-OK</t>
         </is>
       </c>
       <c r="D152" s="15" t="n">
-        <v>0.968</v>
+        <v>0.956</v>
       </c>
       <c r="E152" s="15" t="n">
         <v>0.502</v>
@@ -5115,18 +5214,18 @@
       </c>
       <c r="C156" s="14" t="inlineStr">
         <is>
-          <t>ARTIFICIAIESYSTEM-OK</t>
+          <t>ARTIFICIAIFSYSTEM-OK</t>
         </is>
       </c>
       <c r="D156" s="15" t="n">
-        <v>0.99</v>
+        <v>0.972</v>
       </c>
       <c r="E156" s="15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F156" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.5</v>
+      </c>
+      <c r="F156" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5193,11 +5292,11 @@
       </c>
       <c r="C159" s="18" t="inlineStr">
         <is>
-          <t>EIND-EXTRA-FIND-AOID</t>
+          <t>FIND-EXTRA-FIND-AOID</t>
         </is>
       </c>
       <c r="D159" s="19" t="n">
-        <v>0.962</v>
+        <v>0.968</v>
       </c>
       <c r="E159" s="19" t="n">
         <v>0.508</v>
@@ -5245,11 +5344,11 @@
       </c>
       <c r="C161" s="18" t="inlineStr">
         <is>
-          <t>ABODEFQHIJKLMNOPQRST</t>
+          <t>ABCDEFQHIJKLMNOPQRST</t>
         </is>
       </c>
       <c r="D161" s="19" t="n">
-        <v>0.924</v>
+        <v>0.925</v>
       </c>
       <c r="E161" s="19" t="n">
         <v>0.501</v>
@@ -5275,14 +5374,14 @@
         </is>
       </c>
       <c r="D162" s="15" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
       <c r="E162" s="15" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="F162" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.532</v>
+      </c>
+      <c r="F162" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5297,14 +5396,14 @@
       </c>
       <c r="C163" s="18" t="inlineStr">
         <is>
-          <t>JUMPS-OVER-LAZY-DOG-</t>
+          <t>IVMPS-OVER-LAZY-OOG-</t>
         </is>
       </c>
       <c r="D163" s="19" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="E163" s="19" t="n">
-        <v>0.993</v>
+        <v>0.95</v>
       </c>
       <c r="F163" s="20" t="inlineStr">
         <is>
@@ -5327,14 +5426,14 @@
         </is>
       </c>
       <c r="D164" s="15" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="E164" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F164" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.5</v>
+      </c>
+      <c r="F164" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5349,18 +5448,18 @@
       </c>
       <c r="C165" s="18" t="inlineStr">
         <is>
-          <t>FIVE-DOZEN-LTQUOR-JU</t>
+          <t>FJVF-DOZEN-LIQUOR-IU</t>
         </is>
       </c>
       <c r="D165" s="19" t="n">
-        <v>1</v>
+        <v>0.948</v>
       </c>
       <c r="E165" s="19" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="F165" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.469</v>
+      </c>
+      <c r="F165" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5375,14 +5474,14 @@
       </c>
       <c r="C166" s="14" t="inlineStr">
         <is>
-          <t>PHINX-OF-BLACK-GEM--</t>
+          <t>SPHINX-ON-BLACK-GEM-</t>
         </is>
       </c>
       <c r="D166" s="15" t="n">
-        <v>0.977</v>
+        <v>0.95</v>
       </c>
       <c r="E166" s="15" t="n">
-        <v>0.539</v>
+        <v>0.65</v>
       </c>
       <c r="F166" s="16" t="inlineStr">
         <is>
@@ -5401,14 +5500,14 @@
       </c>
       <c r="C167" s="18" t="inlineStr">
         <is>
-          <t>JUDLE-MY-VOW-GUICKLY</t>
+          <t>IUDGE-MY-VOW-QUICKLT</t>
         </is>
       </c>
       <c r="D167" s="19" t="n">
-        <v>0.95</v>
+        <v>0.973</v>
       </c>
       <c r="E167" s="19" t="n">
-        <v>0.5</v>
+        <v>0.514</v>
       </c>
       <c r="F167" s="16" t="inlineStr">
         <is>
@@ -5427,11 +5526,11 @@
       </c>
       <c r="C168" s="14" t="inlineStr">
         <is>
-          <t>BRIGHTEZEPHYRS-BIOW-</t>
+          <t>BRZGHT-ZFPHYRS-BAOW-</t>
         </is>
       </c>
       <c r="D168" s="15" t="n">
-        <v>0.972</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E168" s="15" t="n">
         <v>0.5</v>
@@ -5453,14 +5552,14 @@
       </c>
       <c r="C169" s="18" t="inlineStr">
         <is>
-          <t>COMPUTER-VISION-TESI</t>
+          <t>COZPVTFR-VISION-TEST</t>
         </is>
       </c>
       <c r="D169" s="19" t="n">
-        <v>0.988</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E169" s="19" t="n">
-        <v>0.758</v>
+        <v>0.445</v>
       </c>
       <c r="F169" s="16" t="inlineStr">
         <is>
@@ -5479,18 +5578,18 @@
       </c>
       <c r="C170" s="14" t="inlineStr">
         <is>
-          <t>MACHINE-LEARNING-AI-</t>
+          <t>MACHZNE-LEARVING-AI-</t>
         </is>
       </c>
       <c r="D170" s="15" t="n">
-        <v>1</v>
+        <v>0.961</v>
       </c>
       <c r="E170" s="15" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="F170" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="F170" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5505,14 +5604,14 @@
       </c>
       <c r="C171" s="18" t="inlineStr">
         <is>
-          <t>DEEP-NEURAL-NETKORKS</t>
+          <t>DEER-NFURAL-NETWORKS</t>
         </is>
       </c>
       <c r="D171" s="19" t="n">
-        <v>0.984</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E171" s="19" t="n">
-        <v>0.68</v>
+        <v>0.442</v>
       </c>
       <c r="F171" s="16" t="inlineStr">
         <is>
@@ -5531,14 +5630,14 @@
       </c>
       <c r="C172" s="14" t="inlineStr">
         <is>
-          <t>TMAGE-DATA-DETECT-OK</t>
+          <t>IMAGE-DQTA-DETECT-CK</t>
         </is>
       </c>
       <c r="D172" s="15" t="n">
-        <v>0.976</v>
+        <v>0.947</v>
       </c>
       <c r="E172" s="15" t="n">
-        <v>0.518</v>
+        <v>0.5</v>
       </c>
       <c r="F172" s="16" t="inlineStr">
         <is>
@@ -5557,18 +5656,18 @@
       </c>
       <c r="C173" s="18" t="inlineStr">
         <is>
-          <t>PYTHON-OPENCV-ROBOT-</t>
+          <t>PYTHON-ODENCV-ROOOT-</t>
         </is>
       </c>
       <c r="D173" s="19" t="n">
-        <v>1</v>
+        <v>0.968</v>
       </c>
       <c r="E173" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.516</v>
+      </c>
+      <c r="F173" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5583,14 +5682,14 @@
       </c>
       <c r="C174" s="14" t="inlineStr">
         <is>
-          <t>SMART-OCR-RECOGNIZE-</t>
+          <t>SMART-OCR-RECOGNIZO-</t>
         </is>
       </c>
       <c r="D174" s="15" t="n">
-        <v>0.991</v>
+        <v>0.99</v>
       </c>
       <c r="E174" s="15" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
@@ -5609,18 +5708,18 @@
       </c>
       <c r="C175" s="18" t="inlineStr">
         <is>
-          <t>ACCURATE-PREDICTION-</t>
+          <t>ACCURATE-PREOICTLON-</t>
         </is>
       </c>
       <c r="D175" s="19" t="n">
-        <v>0.994</v>
+        <v>0.922</v>
       </c>
       <c r="E175" s="19" t="n">
-        <v>0.884</v>
-      </c>
-      <c r="F175" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.5</v>
+      </c>
+      <c r="F175" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5635,14 +5734,14 @@
       </c>
       <c r="C176" s="14" t="inlineStr">
         <is>
-          <t>ARTIFICIAL-SYSTEM-OK</t>
+          <t>ARTIFZCJAL-SYSTEM-OK</t>
         </is>
       </c>
       <c r="D176" s="15" t="n">
-        <v>0.996</v>
+        <v>0.993</v>
       </c>
       <c r="E176" s="15" t="n">
-        <v>0.929</v>
+        <v>0.926</v>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
@@ -5661,18 +5760,18 @@
       </c>
       <c r="C177" s="18" t="inlineStr">
         <is>
-          <t>HELLO-WORLD-WELCOME-</t>
+          <t>HEWLO-WORLD-WELCOME-</t>
         </is>
       </c>
       <c r="D177" s="19" t="n">
-        <v>0.99</v>
+        <v>0.947</v>
       </c>
       <c r="E177" s="19" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="F177" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.456</v>
+      </c>
+      <c r="F177" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5687,14 +5786,14 @@
       </c>
       <c r="C178" s="14" t="inlineStr">
         <is>
-          <t>KNOWLEDGE-IS-POKER--</t>
+          <t>KNOHLSDGE-IS-POWER--</t>
         </is>
       </c>
       <c r="D178" s="15" t="n">
-        <v>0.952</v>
+        <v>0.897</v>
       </c>
       <c r="E178" s="15" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="F178" s="16" t="inlineStr">
         <is>
@@ -5713,14 +5812,14 @@
       </c>
       <c r="C179" s="18" t="inlineStr">
         <is>
-          <t>FIND-EXTRA-FIND-ZOLD</t>
+          <t>LIMD-EXTRA-FIND-GGLD</t>
         </is>
       </c>
       <c r="D179" s="19" t="n">
-        <v>0.974</v>
+        <v>0.92</v>
       </c>
       <c r="E179" s="19" t="n">
-        <v>0.485</v>
+        <v>0.5</v>
       </c>
       <c r="F179" s="16" t="inlineStr">
         <is>
@@ -5739,18 +5838,18 @@
       </c>
       <c r="C180" s="14" t="inlineStr">
         <is>
-          <t>ZERO-ONE-TWO-SIX-TEN</t>
+          <t>ZSRGHONF-TWG-SIK-FEN</t>
         </is>
       </c>
       <c r="D180" s="15" t="n">
-        <v>0.996</v>
+        <v>0.872</v>
       </c>
       <c r="E180" s="15" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="F180" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.457</v>
+      </c>
+      <c r="F180" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5769,19 +5868,1579 @@
         </is>
       </c>
       <c r="D181" s="19" t="n">
-        <v>0.997</v>
+        <v>0.95</v>
       </c>
       <c r="E181" s="19" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="F181" s="20" t="inlineStr">
+        <v>0.517</v>
+      </c>
+      <c r="F181" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B182" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" s="14" t="inlineStr">
+        <is>
+          <t>THE-QUICK-BROWN-FQX-</t>
+        </is>
+      </c>
+      <c r="D182" s="15" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="E182" s="15" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F182" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B183" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C183" s="18" t="inlineStr">
+        <is>
+          <t>JGMAS-OVFR-LAZY-OOI-</t>
+        </is>
+      </c>
+      <c r="D183" s="19" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="E183" s="19" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="F183" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B184" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C184" s="14" t="inlineStr">
+        <is>
+          <t>PACK-MY-BOX-WITE-TEA</t>
+        </is>
+      </c>
+      <c r="D184" s="15" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="F184" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B185" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>FIVEADOZEN-IIQUOR-CU</t>
+        </is>
+      </c>
+      <c r="D185" s="19" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="E185" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F185" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B186" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" s="14" t="inlineStr">
+        <is>
+          <t>SPHLNX-OF-BLACK-GFM-</t>
+        </is>
+      </c>
+      <c r="D186" s="15" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="F186" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B187" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
+        <is>
+          <t>JUDGE-MY-VOW-GUGCKLY</t>
+        </is>
+      </c>
+      <c r="D187" s="19" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="E187" s="19" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F187" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B188" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C188" s="14" t="inlineStr">
+        <is>
+          <t>BXLGUT-ZEPHYRS-BLCX-</t>
+        </is>
+      </c>
+      <c r="D188" s="15" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="E188" s="15" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="F188" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B189" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>CQMPUTER-VISISN-TEST</t>
+        </is>
+      </c>
+      <c r="D189" s="19" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="E189" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F189" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B190" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C190" s="14" t="inlineStr">
+        <is>
+          <t>MACHLNE-LFARNLNG-AL-</t>
+        </is>
+      </c>
+      <c r="D190" s="15" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="E190" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F190" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B191" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>UFEP-NEURAL-NETWQBKS</t>
+        </is>
+      </c>
+      <c r="D191" s="19" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="E191" s="19" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="F191" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B192" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C192" s="14" t="inlineStr">
+        <is>
+          <t>IMAGE-DATA-DFTRCQ-OK</t>
+        </is>
+      </c>
+      <c r="D192" s="15" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="F192" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B193" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>PYTHON-OPENCV-DOBOT-</t>
+        </is>
+      </c>
+      <c r="D193" s="19" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="E193" s="19" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="F193" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B194" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C194" s="14" t="inlineStr">
+        <is>
+          <t>SMART-OCB-RRCOGNIZF-</t>
+        </is>
+      </c>
+      <c r="D194" s="15" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="E194" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F194" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="20" customHeight="1">
+      <c r="A195" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B195" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>ACCUBATE-PREDHCTION-</t>
+        </is>
+      </c>
+      <c r="D195" s="19" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="E195" s="19" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="F195" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B196" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C196" s="14" t="inlineStr">
+        <is>
+          <t>ARTIFUCAAL-REECLCTIO</t>
+        </is>
+      </c>
+      <c r="D196" s="15" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="E196" s="15" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="F196" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1">
+      <c r="A197" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B197" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>HELLO-WORLD-KFLCOME-</t>
+        </is>
+      </c>
+      <c r="D197" s="19" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="E197" s="19" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="F197" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B198" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C198" s="14" t="inlineStr">
+        <is>
+          <t>KNOWLEPGE-LS-POWFR--</t>
+        </is>
+      </c>
+      <c r="D198" s="15" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F198" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B199" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C199" s="18" t="inlineStr">
+        <is>
+          <t>FLND-EXTBA-FLAL-GOIF</t>
+        </is>
+      </c>
+      <c r="D199" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E199" s="19" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="F199" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B200" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C200" s="14" t="inlineStr">
+        <is>
+          <t>ZLBQ-ONE-TWU-CLX-TEN</t>
+        </is>
+      </c>
+      <c r="D200" s="15" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="E200" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F200" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B201" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C201" s="18" t="inlineStr">
+        <is>
+          <t>ABCDEFGHIGKLMNCFGRST</t>
+        </is>
+      </c>
+      <c r="D201" s="19" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="E201" s="19" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B202" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" s="14" t="inlineStr">
+        <is>
+          <t>GHC-RUICK-BROWN-FOX-</t>
+        </is>
+      </c>
+      <c r="D202" s="15" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="E202" s="15" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="F202" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B203" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" s="18" t="inlineStr">
+        <is>
+          <t>JUMPS-OVER-LAZY-DOG-</t>
+        </is>
+      </c>
+      <c r="D203" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1">
+      <c r="A204" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B204" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" s="14" t="inlineStr">
+        <is>
+          <t>PACK-MY-BOX-WITH-TEW</t>
+        </is>
+      </c>
+      <c r="D204" s="15" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="E204" s="15" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F204" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B205" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C205" s="18" t="inlineStr">
+        <is>
+          <t>FIVE-DOZEN-LTQUOR-JU</t>
+        </is>
+      </c>
+      <c r="D205" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" s="19" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="F205" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B206" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C206" s="14" t="inlineStr">
+        <is>
+          <t>SPHINX-OF-BLACK-GEM-</t>
+        </is>
+      </c>
+      <c r="D206" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" s="15" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="F206" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B207" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C207" s="18" t="inlineStr">
+        <is>
+          <t>JUDGE-MY-VOU-GUICKLY</t>
+        </is>
+      </c>
+      <c r="D207" s="19" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="E207" s="19" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1">
+      <c r="A208" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B208" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C208" s="14" t="inlineStr">
+        <is>
+          <t>BRIGHT-ZEPHYRS-BIOW-</t>
+        </is>
+      </c>
+      <c r="D208" s="15" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="E208" s="15" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="F208" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B209" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C209" s="18" t="inlineStr">
+        <is>
+          <t>COMHUTER-VISION-TEST</t>
+        </is>
+      </c>
+      <c r="D209" s="19" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E209" s="19" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F209" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B210" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C210" s="14" t="inlineStr">
+        <is>
+          <t>MACHINE-LEARNING-AI-</t>
+        </is>
+      </c>
+      <c r="D210" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="F210" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1">
+      <c r="A211" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B211" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C211" s="18" t="inlineStr">
+        <is>
+          <t>DEEP-NEURAL-NFTWORKS</t>
+        </is>
+      </c>
+      <c r="D211" s="19" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="E211" s="19" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="F211" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1">
+      <c r="A212" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B212" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C212" s="14" t="inlineStr">
+        <is>
+          <t>IMAGE-DATA-DETECT-OK</t>
+        </is>
+      </c>
+      <c r="D212" s="15" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="E212" s="15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F212" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1">
+      <c r="A213" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B213" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C213" s="18" t="inlineStr">
+        <is>
+          <t>PYTHON-OPENCV-ROBOT-</t>
+        </is>
+      </c>
+      <c r="D213" s="19" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E213" s="19" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="F213" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1">
+      <c r="A214" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B214" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C214" s="14" t="inlineStr">
+        <is>
+          <t>SMART-OCR-RECONNIZE-</t>
+        </is>
+      </c>
+      <c r="D214" s="15" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E214" s="15" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="F214" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1">
+      <c r="A215" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B215" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C215" s="18" t="inlineStr">
+        <is>
+          <t>ACCURATE-PREDICTIOD-</t>
+        </is>
+      </c>
+      <c r="D215" s="19" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E215" s="19" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="F215" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B216" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C216" s="14" t="inlineStr">
+        <is>
+          <t>ARTIFICIAL-SYSTEM-CK</t>
+        </is>
+      </c>
+      <c r="D216" s="15" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E216" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F216" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="20" customHeight="1">
+      <c r="A217" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B217" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C217" s="18" t="inlineStr">
+        <is>
+          <t>HELLO-KORLD-WELCOME-</t>
+        </is>
+      </c>
+      <c r="D217" s="19" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E217" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F217" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1">
+      <c r="A218" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B218" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C218" s="14" t="inlineStr">
+        <is>
+          <t>KNOWLEDGE-IS-POKER--</t>
+        </is>
+      </c>
+      <c r="D218" s="15" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="E218" s="15" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="F218" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1">
+      <c r="A219" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B219" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C219" s="18" t="inlineStr">
+        <is>
+          <t>FIND-EXTRA-FIND-ROLD</t>
+        </is>
+      </c>
+      <c r="D219" s="19" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="E219" s="19" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="F219" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="20" customHeight="1">
+      <c r="A220" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B220" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C220" s="14" t="inlineStr">
+        <is>
+          <t>ZERO-ONE-THO-SIX-TEN</t>
+        </is>
+      </c>
+      <c r="D220" s="15" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E220" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F220" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B221" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C221" s="18" t="inlineStr">
+        <is>
+          <t>ABCDEFGHIJKLMNQPQRST</t>
+        </is>
+      </c>
+      <c r="D221" s="19" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E221" s="19" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="F221" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1">
+      <c r="A222" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B222" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" s="14" t="inlineStr">
+        <is>
+          <t>THE-QUICK-BROWN-FOX-</t>
+        </is>
+      </c>
+      <c r="D222" s="15" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E222" s="15" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="F222" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1">
+      <c r="A223" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B223" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C223" s="18" t="inlineStr">
+        <is>
+          <t>JUMPS-OVER-LAZY-DOG-</t>
+        </is>
+      </c>
+      <c r="D223" s="19" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="E223" s="19" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="F223" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="20" customHeight="1">
+      <c r="A224" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B224" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C224" s="14" t="inlineStr">
+        <is>
+          <t>PACR-MY-BOX-WITH-TEA</t>
+        </is>
+      </c>
+      <c r="D224" s="15" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E224" s="15" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="F224" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="20" customHeight="1">
+      <c r="A225" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B225" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C225" s="18" t="inlineStr">
+        <is>
+          <t>FIVE-DOZEN-LIQUOR-JU</t>
+        </is>
+      </c>
+      <c r="D225" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F225" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="20" customHeight="1">
+      <c r="A226" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B226" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C226" s="14" t="inlineStr">
+        <is>
+          <t>SPHINX-OF-BLACK-GEM-</t>
+        </is>
+      </c>
+      <c r="D226" s="15" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="E226" s="15" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F226" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1">
+      <c r="A227" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B227" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C227" s="18" t="inlineStr">
+        <is>
+          <t>JUDGE-MY-VOW-QUICKLY</t>
+        </is>
+      </c>
+      <c r="D227" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1">
+      <c r="A228" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B228" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C228" s="14" t="inlineStr">
+        <is>
+          <t>BRIGHT-ZEPHYRS-BLOW-</t>
+        </is>
+      </c>
+      <c r="D228" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1">
+      <c r="A229" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B229" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C229" s="18" t="inlineStr">
+        <is>
+          <t>COMPUTER-VISION-TEST</t>
+        </is>
+      </c>
+      <c r="D229" s="19" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E229" s="19" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="F229" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1">
+      <c r="A230" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B230" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C230" s="14" t="inlineStr">
+        <is>
+          <t>MECHINE-LEARNING-AI-</t>
+        </is>
+      </c>
+      <c r="D230" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" s="15" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="F230" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1">
+      <c r="A231" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B231" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C231" s="18" t="inlineStr">
+        <is>
+          <t>DEEP-NEURAL-NETWORKS</t>
+        </is>
+      </c>
+      <c r="D231" s="19" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E231" s="19" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="F231" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1">
+      <c r="A232" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B232" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C232" s="14" t="inlineStr">
+        <is>
+          <t>IMAWE-DATA-OETECT-OK</t>
+        </is>
+      </c>
+      <c r="D232" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E232" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F232" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1">
+      <c r="A233" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B233" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C233" s="18" t="inlineStr">
+        <is>
+          <t>PYTHON-OPENCV-BOBOT-</t>
+        </is>
+      </c>
+      <c r="D233" s="19" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="E233" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F233" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B234" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C234" s="14" t="inlineStr">
+        <is>
+          <t>SMART-OCR-RECOGNIZE-</t>
+        </is>
+      </c>
+      <c r="D234" s="15" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E234" s="15" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="F234" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="20" customHeight="1">
+      <c r="A235" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B235" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C235" s="18" t="inlineStr">
+        <is>
+          <t>ACCURATE-PREDICTION-</t>
+        </is>
+      </c>
+      <c r="D235" s="19" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="E235" s="19" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="F235" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="20" customHeight="1">
+      <c r="A236" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B236" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C236" s="14" t="inlineStr">
+        <is>
+          <t>ARTIFICIAL-SYSTEM-OK</t>
+        </is>
+      </c>
+      <c r="D236" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="20" customHeight="1">
+      <c r="A237" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B237" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C237" s="18" t="inlineStr">
+        <is>
+          <t>HELLO-WORLD-WELCOME-</t>
+        </is>
+      </c>
+      <c r="D237" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F237" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="20" customHeight="1">
+      <c r="A238" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B238" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C238" s="14" t="inlineStr">
+        <is>
+          <t>KNOWLEDGE-IS-POWER--</t>
+        </is>
+      </c>
+      <c r="D238" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E238" s="15" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="F238" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1">
+      <c r="A239" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B239" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C239" s="18" t="inlineStr">
+        <is>
+          <t>FIND-EXTRA-FINO-GOLD</t>
+        </is>
+      </c>
+      <c r="D239" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="20" customHeight="1">
+      <c r="A240" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B240" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C240" s="14" t="inlineStr">
+        <is>
+          <t>ZERO-ONE-TWO-SIX-TEN</t>
+        </is>
+      </c>
+      <c r="D240" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="20" customHeight="1">
+      <c r="A241" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B241" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C241" s="18" t="inlineStr">
+        <is>
+          <t>ABCDEFGHIJKLMNOPQRST</t>
+        </is>
+      </c>
+      <c r="D241" s="19" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E241" s="19" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="F241" s="20" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F181"/>
+  <autoFilter ref="A1:F241"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/results/all_results_ensemble.xlsx
+++ b/outputs/results/all_results_ensemble.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Results" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed_Results'!$A$1:$F$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed_Results'!$A$1:$F$261</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>สร้างรายงานเมื่อ: 2026-10-26 14:43:01 | โมเดลที่ใช้ตรวจ: Dual-Ensemble MLP | ตรวจทั้งหมด: 12 แผ่น | รวม 240 ข้อ</t>
+          <t>สร้างรายงานเมื่อ: 2026-10-28 16:33:13 | โมเดลที่ใช้ตรวจ: Dual-Ensemble MLP | ตรวจทั้งหมด: 13 แผ่น | รวม 260 ข้อ</t>
         </is>
       </c>
     </row>
@@ -676,27 +676,27 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>12 แผ่น</t>
+          <t>13 แผ่น</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>240 ข้อ</t>
+          <t>260 ข้อ</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>4,800 ตัว</t>
+          <t>5,200 ตัว</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>93.04%</t>
+          <t>93.38%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>159 ข้อ</t>
+          <t>174 ข้อ</t>
         </is>
       </c>
     </row>
@@ -1137,6 +1137,39 @@
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>English &amp; Tech (ชุดที่ 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>97.50%</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>0.972</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>15 ข้อ</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>English &amp; Tech (ชุดที่ 1)</t>
         </is>
@@ -1156,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:F261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7439,8 +7472,528 @@
         </is>
       </c>
     </row>
+    <row r="242" ht="20" customHeight="1">
+      <c r="A242" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B242" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="14" t="inlineStr">
+        <is>
+          <t>THE-QUICK-BROWN-FOX-</t>
+        </is>
+      </c>
+      <c r="D242" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E242" s="15" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="F242" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1">
+      <c r="A243" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B243" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C243" s="18" t="inlineStr">
+        <is>
+          <t>JUMPS-OVER-LAZY-DOG-</t>
+        </is>
+      </c>
+      <c r="D243" s="19" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E243" s="19" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="F243" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1">
+      <c r="A244" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B244" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C244" s="14" t="inlineStr">
+        <is>
+          <t>PACK-MY-BOX-WITH-TEA</t>
+        </is>
+      </c>
+      <c r="D244" s="15" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E244" s="15" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="F244" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1">
+      <c r="A245" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B245" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C245" s="18" t="inlineStr">
+        <is>
+          <t>FIVE-DOZEN-LIQUOR-JU</t>
+        </is>
+      </c>
+      <c r="D245" s="19" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="E245" s="19" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="F245" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1">
+      <c r="A246" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B246" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C246" s="14" t="inlineStr">
+        <is>
+          <t>SPHINX-OF-BLACK-GEM-</t>
+        </is>
+      </c>
+      <c r="D246" s="15" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="E246" s="15" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="F246" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1">
+      <c r="A247" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B247" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C247" s="18" t="inlineStr">
+        <is>
+          <t>JUDGE-MY-VOW-QUICKLY</t>
+        </is>
+      </c>
+      <c r="D247" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" s="19" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="F247" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1">
+      <c r="A248" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B248" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C248" s="14" t="inlineStr">
+        <is>
+          <t>BRVGHT-ZEPHYRS-BLOW-</t>
+        </is>
+      </c>
+      <c r="D248" s="15" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E248" s="15" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F248" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1">
+      <c r="A249" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B249" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C249" s="18" t="inlineStr">
+        <is>
+          <t>CONPUTER-VISION-TEST</t>
+        </is>
+      </c>
+      <c r="D249" s="19" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="E249" s="19" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="F249" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1">
+      <c r="A250" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B250" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C250" s="14" t="inlineStr">
+        <is>
+          <t>MECHINE-LEARNING-AI-</t>
+        </is>
+      </c>
+      <c r="D250" s="15" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="E250" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F250" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1">
+      <c r="A251" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B251" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C251" s="18" t="inlineStr">
+        <is>
+          <t>DEEP-NEURAL-NETWORKS</t>
+        </is>
+      </c>
+      <c r="D251" s="19" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="E251" s="19" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="F251" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="20" customHeight="1">
+      <c r="A252" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B252" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C252" s="14" t="inlineStr">
+        <is>
+          <t>IMAGE-DATA-OETECT-OK</t>
+        </is>
+      </c>
+      <c r="D252" s="15" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="E252" s="15" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F252" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1">
+      <c r="A253" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B253" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C253" s="18" t="inlineStr">
+        <is>
+          <t>PYTHON-OPENCV-ROBOT-</t>
+        </is>
+      </c>
+      <c r="D253" s="19" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E253" s="19" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="F253" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1">
+      <c r="A254" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B254" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C254" s="14" t="inlineStr">
+        <is>
+          <t>SMABT-OCR-RECOGNIZE-</t>
+        </is>
+      </c>
+      <c r="D254" s="15" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="E254" s="15" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="F254" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="20" customHeight="1">
+      <c r="A255" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B255" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C255" s="18" t="inlineStr">
+        <is>
+          <t>ACCURATE-PREDICTION-</t>
+        </is>
+      </c>
+      <c r="D255" s="19" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="E255" s="19" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="F255" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="20" customHeight="1">
+      <c r="A256" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C256" s="14" t="inlineStr">
+        <is>
+          <t>ABTIFICIAL-SYSTEM-OK</t>
+        </is>
+      </c>
+      <c r="D256" s="15" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E256" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F256" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="20" customHeight="1">
+      <c r="A257" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B257" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C257" s="18" t="inlineStr">
+        <is>
+          <t>HELLO-WORLD-WELCOME-</t>
+        </is>
+      </c>
+      <c r="D257" s="19" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E257" s="19" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F257" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="20" customHeight="1">
+      <c r="A258" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B258" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C258" s="14" t="inlineStr">
+        <is>
+          <t>KNOWLEDGE-IS-POWER--</t>
+        </is>
+      </c>
+      <c r="D258" s="15" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="E258" s="15" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="F258" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="20" customHeight="1">
+      <c r="A259" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B259" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C259" s="18" t="inlineStr">
+        <is>
+          <t>FVND-EXTRA-FIND-GOLD</t>
+        </is>
+      </c>
+      <c r="D259" s="19" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E259" s="19" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="F259" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="20" customHeight="1">
+      <c r="A260" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B260" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C260" s="14" t="inlineStr">
+        <is>
+          <t>ZERO-ONE-TWO-SIX-TEN</t>
+        </is>
+      </c>
+      <c r="D260" s="15" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="E260" s="15" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="F260" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="20" customHeight="1">
+      <c r="A261" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B261" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C261" s="18" t="inlineStr">
+        <is>
+          <t>OBCDEFJHIJKLMNOPQRST</t>
+        </is>
+      </c>
+      <c r="D261" s="19" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E261" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F261" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F241"/>
+  <autoFilter ref="A1:F261"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>